--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B11" t="n">
-        <v>78852</v>
+        <v>57741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,26 +1577,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1604,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R11" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1642,13 +1647,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1667,10 +1676,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>78852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,31 +1687,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1710,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R12" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1748,17 +1752,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>78852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,31 +1577,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1609,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R11" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1647,17 +1642,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1676,10 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B12" t="n">
-        <v>78852</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,26 +1678,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1714,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R12" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,13 +1748,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>130136203</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130126980</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130126997</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>130126990</v>
       </c>
       <c r="B5" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>130127016</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>130127015</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>130126996</v>
       </c>
       <c r="B8" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>130127014</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130127017</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B11" t="n">
-        <v>78852</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,26 +1577,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1604,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R11" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1642,13 +1647,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1667,10 +1676,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>78937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,31 +1687,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1710,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R12" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1748,17 +1752,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>130136265</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>130136203</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>130136259</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>130136229</v>
       </c>
       <c r="B17" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>78937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,31 +1577,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1609,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R11" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1647,17 +1642,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1676,10 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B12" t="n">
-        <v>78937</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,26 +1678,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1714,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R12" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,13 +1748,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B11" t="n">
-        <v>78937</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,26 +1577,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1604,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R11" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1642,13 +1647,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1667,10 +1676,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>78937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,31 +1687,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1710,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R12" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1748,17 +1752,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130126997</v>
       </c>
       <c r="B3" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>130126990</v>
       </c>
       <c r="B5" t="n">
-        <v>78938</v>
+        <v>78941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>130127016</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>130127015</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>130126996</v>
       </c>
       <c r="B8" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>130127014</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130127017</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>78940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,31 +1577,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1609,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R11" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1647,17 +1642,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1676,10 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B12" t="n">
-        <v>78937</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,26 +1678,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1714,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R12" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,13 +1748,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>130136265</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>130136203</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>130136259</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>130136229</v>
       </c>
       <c r="B17" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130126980</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130126997</v>
       </c>
       <c r="B3" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>130126990</v>
       </c>
       <c r="B5" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>130127016</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>130127015</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>130126996</v>
       </c>
       <c r="B8" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>130127014</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130127017</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B11" t="n">
-        <v>78940</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,26 +1577,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1604,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R11" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1642,13 +1647,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1667,10 +1676,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>78966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,31 +1687,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1710,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R12" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1748,17 +1752,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>130136265</v>
       </c>
       <c r="B13" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>130136203</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>130136259</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>130136229</v>
       </c>
       <c r="B17" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>78966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,31 +1577,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1609,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R11" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1647,17 +1642,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1676,10 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B12" t="n">
-        <v>78966</v>
+        <v>57852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,26 +1678,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1714,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R12" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1752,13 +1748,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136225</v>
+        <v>130136183</v>
       </c>
       <c r="B11" t="n">
-        <v>78966</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,26 +1577,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1604,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491040</v>
+        <v>490950</v>
       </c>
       <c r="R11" t="n">
-        <v>6679160</v>
+        <v>6679172</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1642,13 +1647,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1667,10 +1676,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136183</v>
+        <v>130136225</v>
       </c>
       <c r="B12" t="n">
-        <v>57852</v>
+        <v>78966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,31 +1687,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1710,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490950</v>
+        <v>491040</v>
       </c>
       <c r="R12" t="n">
-        <v>6679172</v>
+        <v>6679160</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1748,17 +1752,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>130136203</v>
       </c>
       <c r="B15" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59946-2025 artfynd.xlsx
+++ b/artfynd/A 59946-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130126980</v>
+        <v>130127014</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490883</v>
+        <v>490977</v>
       </c>
       <c r="R2" t="n">
-        <v>6679123</v>
+        <v>6679172</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130126997</v>
+        <v>130127015</v>
       </c>
       <c r="B3" t="n">
-        <v>78966</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491003</v>
+        <v>490949</v>
       </c>
       <c r="R3" t="n">
-        <v>6679174</v>
+        <v>6679162</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130126992</v>
+        <v>130127016</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491058</v>
+        <v>490951</v>
       </c>
       <c r="R4" t="n">
-        <v>6679182</v>
+        <v>6679140</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -953,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130126990</v>
+        <v>130127017</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490890</v>
+        <v>490956</v>
       </c>
       <c r="R5" t="n">
-        <v>6679136</v>
+        <v>6679151</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130127016</v>
+        <v>130136259</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1110,19 +1092,22 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490951</v>
+        <v>491057</v>
       </c>
       <c r="R6" t="n">
-        <v>6679140</v>
+        <v>6679172</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1146,12 +1131,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,32 +1145,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130127015</v>
+        <v>130136265</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1207,19 +1193,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490949</v>
+        <v>491066</v>
       </c>
       <c r="R7" t="n">
-        <v>6679162</v>
+        <v>6679169</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1243,12 +1232,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,18 +1246,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1278,7 +1268,7 @@
         <v>130126996</v>
       </c>
       <c r="B8" t="n">
-        <v>78966</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130127014</v>
+        <v>130126997</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490977</v>
+        <v>491003</v>
       </c>
       <c r="R9" t="n">
-        <v>6679172</v>
+        <v>6679174</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1469,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130127017</v>
+        <v>130136225</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,37 +1470,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490956</v>
+        <v>491040</v>
       </c>
       <c r="R10" t="n">
-        <v>6679151</v>
+        <v>6679160</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1534,12 +1527,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1548,28 +1541,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130136183</v>
+        <v>130136229</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,31 +1571,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1609,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490950</v>
+        <v>491051</v>
       </c>
       <c r="R11" t="n">
-        <v>6679172</v>
+        <v>6679163</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1647,17 +1636,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1676,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130136225</v>
+        <v>130126980</v>
       </c>
       <c r="B12" t="n">
-        <v>78966</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,26 +1672,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1714,13 +1704,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491040</v>
+        <v>490883</v>
       </c>
       <c r="R12" t="n">
-        <v>6679160</v>
+        <v>6679123</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1744,12 +1734,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1758,29 +1753,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130136265</v>
+        <v>130136183</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,26 +1782,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1815,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491066</v>
+        <v>490950</v>
       </c>
       <c r="R13" t="n">
-        <v>6679169</v>
+        <v>6679172</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1853,13 +1852,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1878,10 +1881,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130136351</v>
+        <v>130126992</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1907,28 +1910,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491088</v>
+        <v>491058</v>
       </c>
       <c r="R14" t="n">
-        <v>6679194</v>
+        <v>6679182</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1952,12 +1946,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,65 +1965,61 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130136203</v>
+        <v>130136351</v>
       </c>
       <c r="B15" t="n">
-        <v>98950</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490964</v>
+        <v>491088</v>
       </c>
       <c r="R15" t="n">
-        <v>6679165</v>
+        <v>6679194</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2095,37 +2090,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130136259</v>
+        <v>130136203</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2133,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491057</v>
+        <v>490964</v>
       </c>
       <c r="R16" t="n">
-        <v>6679172</v>
+        <v>6679165</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2196,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130136229</v>
+        <v>130126990</v>
       </c>
       <c r="B17" t="n">
-        <v>78966</v>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2207,40 +2211,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491051</v>
+        <v>490890</v>
       </c>
       <c r="R17" t="n">
-        <v>6679163</v>
+        <v>6679136</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2264,12 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2278,19 +2279,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
